--- a/laporan_padel_dki_jakarta_2026-10-30.xlsx
+++ b/laporan_padel_dki_jakarta_2026-10-30.xlsx
@@ -7734,16 +7734,16 @@
         <v>170</v>
       </c>
       <c r="D38" t="n">
-        <v>122</v>
+        <v>124</v>
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>28.2%</t>
+          <t>27.1%</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Rp6.000.000</t>
+          <t>Rp5.900.000</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
@@ -8963,16 +8963,16 @@
         <v>54</v>
       </c>
       <c r="D24" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>53.7%</t>
+          <t>55.6%</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Rp4.149.993</t>
+          <t>Rp4.274.993</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
@@ -9335,16 +9335,16 @@
         <v>72</v>
       </c>
       <c r="D36" t="n">
-        <v>54</v>
+        <v>50</v>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>25.0%</t>
+          <t>30.6%</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Rp1.684.000</t>
+          <t>Rp1.982.000</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">

--- a/laporan_padel_dki_jakarta_2026-10-30.xlsx
+++ b/laporan_padel_dki_jakarta_2026-10-30.xlsx
@@ -575,16 +575,16 @@
         <v>80</v>
       </c>
       <c r="D5" t="n">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>20.0%</t>
+          <t>21.2%</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Rp1.941.000</t>
+          <t>Rp2.040.000</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
@@ -606,16 +606,16 @@
         <v>34</v>
       </c>
       <c r="D6" t="n">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>38.2%</t>
+          <t>44.1%</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Rp2.017.000</t>
+          <t>Rp2.415.000</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
@@ -668,16 +668,16 @@
         <v>64</v>
       </c>
       <c r="D8" t="n">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>43.8%</t>
+          <t>40.6%</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Rp5.760.000</t>
+          <t>Rp5.280.000</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
@@ -730,16 +730,16 @@
         <v>72</v>
       </c>
       <c r="D10" t="n">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>33.3%</t>
+          <t>36.1%</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Rp6.215.988</t>
+          <t>Rp6.553.988</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
@@ -1164,16 +1164,16 @@
         <v>144</v>
       </c>
       <c r="D24" t="n">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>16.7%</t>
+          <t>17.4%</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Rp4.400.000</t>
+          <t>Rp4.550.000</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
@@ -1195,16 +1195,16 @@
         <v>72</v>
       </c>
       <c r="D25" t="n">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>20.8%</t>
+          <t>22.2%</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Rp2.825.000</t>
+          <t>Rp2.950.000</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
@@ -1226,16 +1226,16 @@
         <v>68</v>
       </c>
       <c r="D26" t="n">
-        <v>54</v>
+        <v>57</v>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>20.6%</t>
+          <t>16.2%</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Rp2.040.000</t>
+          <t>Rp1.740.000</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
@@ -1381,16 +1381,16 @@
         <v>102</v>
       </c>
       <c r="D31" t="n">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>37.3%</t>
+          <t>38.2%</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Rp4.222.000</t>
+          <t>Rp4.292.000</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
@@ -1598,16 +1598,16 @@
         <v>64</v>
       </c>
       <c r="D38" t="n">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>45.3%</t>
+          <t>46.9%</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Rp5.970.000</t>
+          <t>Rp6.140.000</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
@@ -1722,16 +1722,16 @@
         <v>51</v>
       </c>
       <c r="D42" t="n">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>31.4%</t>
+          <t>33.3%</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Rp2.370.000</t>
+          <t>Rp2.445.000</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
@@ -1753,16 +1753,16 @@
         <v>234</v>
       </c>
       <c r="D43" t="n">
-        <v>216</v>
+        <v>218</v>
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>7.7%</t>
+          <t>6.8%</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Rp4.185.000</t>
+          <t>Rp3.787.000</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
@@ -2218,16 +2218,16 @@
         <v>54</v>
       </c>
       <c r="D58" t="n">
-        <v>49</v>
+        <v>45</v>
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>9.3%</t>
+          <t>16.7%</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Rp595.000</t>
+          <t>Rp915.000</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
@@ -2342,16 +2342,16 @@
         <v>90</v>
       </c>
       <c r="D62" t="n">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>44.4%</t>
+          <t>45.6%</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Rp8.480.000</t>
+          <t>Rp8.700.000</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
@@ -2683,16 +2683,16 @@
         <v>72</v>
       </c>
       <c r="D73" t="n">
-        <v>64</v>
+        <v>66</v>
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>11.1%</t>
+          <t>8.3%</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Rp885.000</t>
+          <t>Rp545.000</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
@@ -2745,16 +2745,16 @@
         <v>96</v>
       </c>
       <c r="D75" t="n">
-        <v>80</v>
+        <v>82</v>
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>16.7%</t>
+          <t>14.6%</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Rp3.160.000</t>
+          <t>Rp2.640.000</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
@@ -2838,16 +2838,16 @@
         <v>128</v>
       </c>
       <c r="D78" t="n">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>24.2%</t>
+          <t>25.0%</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>Rp6.045.000</t>
+          <t>Rp6.225.000</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
@@ -2869,16 +2869,16 @@
         <v>108</v>
       </c>
       <c r="D79" t="n">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>12.0%</t>
+          <t>13.0%</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>Rp1.575.000</t>
+          <t>Rp1.650.000</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
@@ -3024,16 +3024,16 @@
         <v>14</v>
       </c>
       <c r="D84" t="n">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>14.3%</t>
+          <t>35.7%</t>
         </is>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>Rp650.000</t>
+          <t>Rp2.000.000</t>
         </is>
       </c>
       <c r="G84" t="inlineStr">
@@ -3179,16 +3179,16 @@
         <v>138</v>
       </c>
       <c r="D89" t="n">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t>15.9%</t>
+          <t>16.7%</t>
         </is>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>Rp4.025.000</t>
+          <t>Rp4.175.000</t>
         </is>
       </c>
       <c r="G89" t="inlineStr">
@@ -3303,16 +3303,16 @@
         <v>42</v>
       </c>
       <c r="D93" t="n">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="E93" t="inlineStr">
         <is>
-          <t>14.3%</t>
+          <t>16.7%</t>
         </is>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>Rp594.000</t>
+          <t>Rp693.000</t>
         </is>
       </c>
       <c r="G93" t="inlineStr">
@@ -3458,16 +3458,16 @@
         <v>112</v>
       </c>
       <c r="D98" t="n">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="E98" t="inlineStr">
         <is>
-          <t>13.4%</t>
+          <t>14.3%</t>
         </is>
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>Rp1.655.000</t>
+          <t>Rp1.780.000</t>
         </is>
       </c>
       <c r="G98" t="inlineStr">
@@ -3819,16 +3819,16 @@
         <v>162</v>
       </c>
       <c r="D7" t="n">
-        <v>122</v>
+        <v>118</v>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>24.7%</t>
+          <t>27.2%</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Rp6.660.000</t>
+          <t>Rp7.215.000</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
@@ -3881,16 +3881,16 @@
         <v>64</v>
       </c>
       <c r="D9" t="n">
-        <v>31</v>
+        <v>27</v>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>51.6%</t>
+          <t>57.8%</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Rp3.605.000</t>
+          <t>Rp4.005.000</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
@@ -3974,16 +3974,16 @@
         <v>51</v>
       </c>
       <c r="D12" t="n">
-        <v>35</v>
+        <v>33</v>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>31.4%</t>
+          <t>35.3%</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Rp4.475.000</t>
+          <t>Rp4.855.000</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
@@ -4169,12 +4169,12 @@
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Rp5.850.000</t>
+          <t>Rp5.080.000</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Rp200.000 - Rp300.000</t>
+          <t>Rp160.000 - Rp260.000</t>
         </is>
       </c>
     </row>
@@ -4439,16 +4439,16 @@
         <v>45</v>
       </c>
       <c r="D27" t="n">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>48.9%</t>
+          <t>53.3%</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Rp6.028.000</t>
+          <t>Rp6.526.000</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
@@ -4501,16 +4501,16 @@
         <v>36</v>
       </c>
       <c r="D29" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>38.9%</t>
+          <t>36.1%</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Rp4.000.000</t>
+          <t>Rp3.750.000</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
@@ -4687,16 +4687,16 @@
         <v>70</v>
       </c>
       <c r="D35" t="n">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>15.7%</t>
+          <t>17.1%</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Rp1.980.000</t>
+          <t>Rp2.110.000</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
@@ -4749,16 +4749,16 @@
         <v>159</v>
       </c>
       <c r="D37" t="n">
-        <v>94</v>
+        <v>91</v>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>40.9%</t>
+          <t>42.8%</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Rp22.600.000</t>
+          <t>Rp23.200.000</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
@@ -5059,16 +5059,16 @@
         <v>6</v>
       </c>
       <c r="D47" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>0.0%</t>
+          <t>33.3%</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Rp0</t>
+          <t>Rp2.700.000</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
@@ -5121,16 +5121,16 @@
         <v>80</v>
       </c>
       <c r="D49" t="n">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>42.5%</t>
+          <t>45.0%</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Rp5.350.000</t>
+          <t>Rp5.600.000</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
@@ -5369,16 +5369,16 @@
         <v>75</v>
       </c>
       <c r="D57" t="n">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>2.7%</t>
+          <t>4.0%</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Rp124.000</t>
+          <t>Rp195.000</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
@@ -5431,16 +5431,16 @@
         <v>124</v>
       </c>
       <c r="D59" t="n">
-        <v>111</v>
+        <v>109</v>
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>10.5%</t>
+          <t>12.1%</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Rp1.420.000</t>
+          <t>Rp1.620.000</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
@@ -5679,16 +5679,16 @@
         <v>234</v>
       </c>
       <c r="D67" t="n">
-        <v>149</v>
+        <v>147</v>
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>36.3%</t>
+          <t>37.2%</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Rp9.832.000</t>
+          <t>Rp10.132.000</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
@@ -5834,16 +5834,16 @@
         <v>162</v>
       </c>
       <c r="D72" t="n">
-        <v>116</v>
+        <v>114</v>
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>28.4%</t>
+          <t>29.6%</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Rp22.300.000</t>
+          <t>Rp23.200.000</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
@@ -6040,16 +6040,16 @@
         <v>108</v>
       </c>
       <c r="D5" t="n">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>20.4%</t>
+          <t>21.3%</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Rp7.300.000</t>
+          <t>Rp7.650.000</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
@@ -6102,16 +6102,16 @@
         <v>68</v>
       </c>
       <c r="D7" t="n">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>17.6%</t>
+          <t>19.1%</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Rp1.200.000</t>
+          <t>Rp1.270.000</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
@@ -6195,16 +6195,16 @@
         <v>42</v>
       </c>
       <c r="D10" t="n">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>47.6%</t>
+          <t>52.4%</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Rp5.100.000</t>
+          <t>Rp5.400.000</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
@@ -6618,16 +6618,16 @@
         <v>186</v>
       </c>
       <c r="D2" t="n">
-        <v>141</v>
+        <v>138</v>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>24.2%</t>
+          <t>25.8%</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Rp13.210.000</t>
+          <t>Rp13.470.000</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
@@ -6711,16 +6711,16 @@
         <v>90</v>
       </c>
       <c r="D5" t="n">
-        <v>87</v>
+        <v>85</v>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>3.3%</t>
+          <t>5.6%</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Rp267.000</t>
+          <t>Rp565.000</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
@@ -6959,16 +6959,16 @@
         <v>42</v>
       </c>
       <c r="D13" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>59.5%</t>
+          <t>61.9%</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Rp7.102.000</t>
+          <t>Rp7.290.000</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
@@ -7021,16 +7021,16 @@
         <v>102</v>
       </c>
       <c r="D15" t="n">
-        <v>83</v>
+        <v>81</v>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>18.6%</t>
+          <t>20.6%</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Rp3.615.000</t>
+          <t>Rp4.365.000</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
@@ -7052,16 +7052,16 @@
         <v>108</v>
       </c>
       <c r="D16" t="n">
-        <v>75</v>
+        <v>73</v>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>30.6%</t>
+          <t>32.4%</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Rp6.050.000</t>
+          <t>Rp6.450.000</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
@@ -7083,16 +7083,16 @@
         <v>144</v>
       </c>
       <c r="D17" t="n">
-        <v>135</v>
+        <v>131</v>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>6.2%</t>
+          <t>9.0%</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Rp1.700.000</t>
+          <t>Rp2.800.000</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
@@ -7114,16 +7114,16 @@
         <v>90</v>
       </c>
       <c r="D18" t="n">
-        <v>79</v>
+        <v>77</v>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>12.2%</t>
+          <t>14.4%</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Rp1.850.000</t>
+          <t>Rp2.350.000</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
@@ -7362,16 +7362,16 @@
         <v>108</v>
       </c>
       <c r="D26" t="n">
-        <v>89</v>
+        <v>87</v>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>17.6%</t>
+          <t>19.4%</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Rp4.110.000</t>
+          <t>Rp4.610.000</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
@@ -7579,16 +7579,16 @@
         <v>72</v>
       </c>
       <c r="D33" t="n">
-        <v>67</v>
+        <v>63</v>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>6.9%</t>
+          <t>12.5%</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Rp1.265.000</t>
+          <t>Rp2.405.000</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
@@ -7641,16 +7641,16 @@
         <v>187</v>
       </c>
       <c r="D35" t="n">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>56.1%</t>
+          <t>56.7%</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Rp17.950.000</t>
+          <t>Rp18.000.000</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
@@ -7827,16 +7827,16 @@
         <v>150</v>
       </c>
       <c r="D41" t="n">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>54.0%</t>
+          <t>54.7%</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Rp24.475.000</t>
+          <t>Rp24.700.000</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
@@ -7858,16 +7858,16 @@
         <v>112</v>
       </c>
       <c r="D42" t="n">
-        <v>95</v>
+        <v>91</v>
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>15.2%</t>
+          <t>18.8%</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Rp6.650.000</t>
+          <t>Rp8.200.000</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
@@ -7951,16 +7951,16 @@
         <v>112</v>
       </c>
       <c r="D45" t="n">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>37.5%</t>
+          <t>38.4%</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Rp9.880.000</t>
+          <t>Rp10.105.000</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
@@ -7982,16 +7982,16 @@
         <v>174</v>
       </c>
       <c r="D46" t="n">
-        <v>107</v>
+        <v>105</v>
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>38.5%</t>
+          <t>39.7%</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Rp28.500.000</t>
+          <t>Rp29.500.000</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
@@ -8137,16 +8137,16 @@
         <v>98</v>
       </c>
       <c r="D51" t="n">
-        <v>69</v>
+        <v>65</v>
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>29.6%</t>
+          <t>33.7%</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Rp7.390.000</t>
+          <t>Rp8.370.000</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
@@ -8168,16 +8168,16 @@
         <v>144</v>
       </c>
       <c r="D52" t="n">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>22.9%</t>
+          <t>23.6%</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Rp5.600.000</t>
+          <t>Rp5.725.000</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
@@ -8312,16 +8312,16 @@
         <v>136</v>
       </c>
       <c r="D3" t="n">
-        <v>79</v>
+        <v>73</v>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>41.9%</t>
+          <t>46.3%</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Rp9.785.000</t>
+          <t>Rp10.385.000</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
@@ -8374,16 +8374,16 @@
         <v>86</v>
       </c>
       <c r="D5" t="n">
-        <v>67</v>
+        <v>65</v>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>22.1%</t>
+          <t>24.4%</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Rp5.350.000</t>
+          <t>Rp6.050.000</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
@@ -8467,16 +8467,16 @@
         <v>51</v>
       </c>
       <c r="D8" t="n">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>17.6%</t>
+          <t>19.6%</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Rp1.350.000</t>
+          <t>Rp1.535.000</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
@@ -8622,16 +8622,16 @@
         <v>54</v>
       </c>
       <c r="D13" t="n">
-        <v>32</v>
+        <v>35</v>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>40.7%</t>
+          <t>35.2%</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Rp3.499.990</t>
+          <t>Rp3.124.990</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
@@ -8808,16 +8808,16 @@
         <v>108</v>
       </c>
       <c r="D19" t="n">
-        <v>40</v>
+        <v>34</v>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>63.0%</t>
+          <t>68.5%</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Rp25.570.000</t>
+          <t>Rp27.510.000</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
@@ -9025,16 +9025,16 @@
         <v>54</v>
       </c>
       <c r="D26" t="n">
-        <v>23</v>
+        <v>17</v>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>57.4%</t>
+          <t>68.5%</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Rp4.650.000</t>
+          <t>Rp5.550.000</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
@@ -9087,16 +9087,16 @@
         <v>36</v>
       </c>
       <c r="D28" t="n">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>44.4%</t>
+          <t>50.0%</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Rp3.350.000</t>
+          <t>Rp3.850.000</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
@@ -9118,16 +9118,16 @@
         <v>32</v>
       </c>
       <c r="D29" t="n">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>53.1%</t>
+          <t>62.5%</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Rp2.325.000</t>
+          <t>Rp2.700.000</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
@@ -9242,16 +9242,16 @@
         <v>36</v>
       </c>
       <c r="D33" t="n">
-        <v>21</v>
+        <v>18</v>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>41.7%</t>
+          <t>50.0%</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Rp2.600.000</t>
+          <t>Rp2.900.000</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
@@ -9366,16 +9366,16 @@
         <v>54</v>
       </c>
       <c r="D37" t="n">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>35.2%</t>
+          <t>33.3%</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Rp3.795.000</t>
+          <t>Rp3.610.000</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">

--- a/laporan_padel_dki_jakarta_2026-10-30.xlsx
+++ b/laporan_padel_dki_jakarta_2026-10-30.xlsx
@@ -544,16 +544,16 @@
         <v>168</v>
       </c>
       <c r="D4" t="n">
-        <v>138</v>
+        <v>134</v>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>17.9%</t>
+          <t>20.2%</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Rp15.520.000</t>
+          <t>Rp16.380.000</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
@@ -575,16 +575,16 @@
         <v>80</v>
       </c>
       <c r="D5" t="n">
-        <v>63</v>
+        <v>61</v>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>21.2%</t>
+          <t>23.8%</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Rp2.040.000</t>
+          <t>Rp2.340.000</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
@@ -730,16 +730,16 @@
         <v>72</v>
       </c>
       <c r="D10" t="n">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>36.1%</t>
+          <t>33.3%</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Rp6.553.988</t>
+          <t>Rp5.855.990</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
@@ -792,16 +792,16 @@
         <v>96</v>
       </c>
       <c r="D12" t="n">
-        <v>52</v>
+        <v>58</v>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>45.8%</t>
+          <t>39.6%</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Rp12.160.000</t>
+          <t>Rp10.660.000</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
@@ -863,7 +863,7 @@
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Rp11.327.000</t>
+          <t>Rp11.519.500</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
@@ -947,16 +947,16 @@
         <v>68</v>
       </c>
       <c r="D17" t="n">
-        <v>68</v>
+        <v>62</v>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>0.0%</t>
+          <t>8.8%</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Rp0</t>
+          <t>Rp900.000</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
@@ -1071,16 +1071,16 @@
         <v>136</v>
       </c>
       <c r="D21" t="n">
-        <v>99</v>
+        <v>97</v>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>27.2%</t>
+          <t>28.7%</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Rp10.560.000</t>
+          <t>Rp11.050.000</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
@@ -1195,16 +1195,16 @@
         <v>72</v>
       </c>
       <c r="D25" t="n">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>22.2%</t>
+          <t>23.6%</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Rp2.950.000</t>
+          <t>Rp3.075.000</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
@@ -1226,16 +1226,16 @@
         <v>68</v>
       </c>
       <c r="D26" t="n">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>16.2%</t>
+          <t>14.7%</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Rp1.740.000</t>
+          <t>Rp1.615.000</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
@@ -1505,16 +1505,16 @@
         <v>72</v>
       </c>
       <c r="D35" t="n">
-        <v>50</v>
+        <v>47</v>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>30.6%</t>
+          <t>34.7%</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Rp2.936.000</t>
+          <t>Rp3.320.000</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
@@ -1722,16 +1722,16 @@
         <v>51</v>
       </c>
       <c r="D42" t="n">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>33.3%</t>
+          <t>29.4%</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Rp2.445.000</t>
+          <t>Rp2.105.000</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
@@ -2001,16 +2001,16 @@
         <v>56</v>
       </c>
       <c r="D51" t="n">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>5.4%</t>
+          <t>7.1%</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Rp1.375.000</t>
+          <t>Rp1.925.000</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
@@ -2032,16 +2032,16 @@
         <v>64</v>
       </c>
       <c r="D52" t="n">
-        <v>63</v>
+        <v>61</v>
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>1.6%</t>
+          <t>4.7%</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Rp288.000</t>
+          <t>Rp864.000</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
@@ -2108,7 +2108,7 @@
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Rp96.000 - Rp120.000</t>
+          <t>Rp80.000 - Rp120.000</t>
         </is>
       </c>
     </row>
@@ -2187,16 +2187,16 @@
         <v>48</v>
       </c>
       <c r="D57" t="n">
-        <v>44</v>
+        <v>48</v>
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>8.3%</t>
+          <t>0.0%</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Rp720.000</t>
+          <t>Rp0</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
@@ -2311,16 +2311,16 @@
         <v>80</v>
       </c>
       <c r="D61" t="n">
-        <v>75</v>
+        <v>73</v>
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>6.2%</t>
+          <t>8.8%</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Rp510.000</t>
+          <t>Rp870.000</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
@@ -2342,16 +2342,16 @@
         <v>90</v>
       </c>
       <c r="D62" t="n">
-        <v>49</v>
+        <v>47</v>
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>45.6%</t>
+          <t>47.8%</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Rp8.700.000</t>
+          <t>Rp8.780.000</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
@@ -2373,16 +2373,16 @@
         <v>72</v>
       </c>
       <c r="D63" t="n">
-        <v>59</v>
+        <v>55</v>
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>18.1%</t>
+          <t>23.6%</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Rp1.715.000</t>
+          <t>Rp2.355.000</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
@@ -2683,16 +2683,16 @@
         <v>72</v>
       </c>
       <c r="D73" t="n">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>8.3%</t>
+          <t>9.7%</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Rp545.000</t>
+          <t>Rp620.000</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
@@ -2776,16 +2776,16 @@
         <v>98</v>
       </c>
       <c r="D76" t="n">
-        <v>88</v>
+        <v>86</v>
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>10.2%</t>
+          <t>12.2%</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Rp1.750.000</t>
+          <t>Rp2.350.000</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
@@ -2869,16 +2869,16 @@
         <v>108</v>
       </c>
       <c r="D79" t="n">
-        <v>94</v>
+        <v>92</v>
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>13.0%</t>
+          <t>14.8%</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>Rp1.650.000</t>
+          <t>Rp1.800.000</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
@@ -2900,16 +2900,16 @@
         <v>114</v>
       </c>
       <c r="D80" t="n">
-        <v>111</v>
+        <v>109</v>
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>2.6%</t>
+          <t>4.4%</t>
         </is>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>Rp850.000</t>
+          <t>Rp1.850.000</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
@@ -2931,16 +2931,16 @@
         <v>126</v>
       </c>
       <c r="D81" t="n">
-        <v>108</v>
+        <v>100</v>
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>14.3%</t>
+          <t>20.6%</t>
         </is>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>Rp2.382.000</t>
+          <t>Rp3.774.000</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
@@ -3086,16 +3086,16 @@
         <v>108</v>
       </c>
       <c r="D86" t="n">
-        <v>87</v>
+        <v>96</v>
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>19.4%</t>
+          <t>11.1%</t>
         </is>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>Rp4.700.000</t>
+          <t>Rp3.200.000</t>
         </is>
       </c>
       <c r="G86" t="inlineStr">
@@ -3179,16 +3179,16 @@
         <v>138</v>
       </c>
       <c r="D89" t="n">
-        <v>115</v>
+        <v>111</v>
       </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t>16.7%</t>
+          <t>19.6%</t>
         </is>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>Rp4.175.000</t>
+          <t>Rp5.075.000</t>
         </is>
       </c>
       <c r="G89" t="inlineStr">
@@ -3210,16 +3210,16 @@
         <v>90</v>
       </c>
       <c r="D90" t="n">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="E90" t="inlineStr">
         <is>
-          <t>15.6%</t>
+          <t>16.7%</t>
         </is>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>Rp2.044.900</t>
+          <t>Rp2.143.900</t>
         </is>
       </c>
       <c r="G90" t="inlineStr">
@@ -3396,16 +3396,16 @@
         <v>80</v>
       </c>
       <c r="D96" t="n">
-        <v>60</v>
+        <v>58</v>
       </c>
       <c r="E96" t="inlineStr">
         <is>
-          <t>25.0%</t>
+          <t>27.5%</t>
         </is>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>Rp3.980.000</t>
+          <t>Rp4.278.000</t>
         </is>
       </c>
       <c r="G96" t="inlineStr">
@@ -3458,16 +3458,16 @@
         <v>112</v>
       </c>
       <c r="D98" t="n">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="E98" t="inlineStr">
         <is>
-          <t>14.3%</t>
+          <t>15.2%</t>
         </is>
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>Rp1.780.000</t>
+          <t>Rp1.880.000</t>
         </is>
       </c>
       <c r="G98" t="inlineStr">
@@ -3551,16 +3551,16 @@
         <v>28</v>
       </c>
       <c r="D101" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="E101" t="inlineStr">
         <is>
-          <t>25.0%</t>
+          <t>28.6%</t>
         </is>
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>Rp1.625.000</t>
+          <t>Rp2.025.000</t>
         </is>
       </c>
       <c r="G101" t="inlineStr">
@@ -3664,16 +3664,16 @@
         <v>36</v>
       </c>
       <c r="D2" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>41.7%</t>
+          <t>44.4%</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Rp1.215.000</t>
+          <t>Rp1.296.000</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
@@ -3757,16 +3757,16 @@
         <v>96</v>
       </c>
       <c r="D5" t="n">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>17.7%</t>
+          <t>18.8%</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Rp4.450.000</t>
+          <t>Rp4.700.000</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
@@ -3819,16 +3819,16 @@
         <v>162</v>
       </c>
       <c r="D7" t="n">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>27.2%</t>
+          <t>27.8%</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Rp7.215.000</t>
+          <t>Rp7.365.000</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
@@ -3881,16 +3881,16 @@
         <v>64</v>
       </c>
       <c r="D9" t="n">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>57.8%</t>
+          <t>59.4%</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Rp4.005.000</t>
+          <t>Rp4.180.000</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
@@ -3943,16 +3943,16 @@
         <v>16</v>
       </c>
       <c r="D11" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>62.5%</t>
+          <t>75.0%</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Rp900.000</t>
+          <t>Rp1.080.000</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
@@ -4005,16 +4005,16 @@
         <v>59</v>
       </c>
       <c r="D13" t="n">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>32.2%</t>
+          <t>33.9%</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Rp5.350.000</t>
+          <t>Rp5.535.000</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
@@ -4067,16 +4067,16 @@
         <v>48</v>
       </c>
       <c r="D15" t="n">
-        <v>21</v>
+        <v>18</v>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>56.2%</t>
+          <t>62.5%</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Rp5.120.000</t>
+          <t>Rp5.480.000</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
@@ -4098,16 +4098,16 @@
         <v>105</v>
       </c>
       <c r="D16" t="n">
-        <v>88</v>
+        <v>85</v>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>16.2%</t>
+          <t>19.0%</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Rp7.050.000</t>
+          <t>Rp8.400.000</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
@@ -4160,16 +4160,16 @@
         <v>54</v>
       </c>
       <c r="D18" t="n">
-        <v>30</v>
+        <v>27</v>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>44.4%</t>
+          <t>50.0%</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Rp5.080.000</t>
+          <t>Rp5.560.000</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
@@ -4284,16 +4284,16 @@
         <v>34</v>
       </c>
       <c r="D22" t="n">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>14.7%</t>
+          <t>20.6%</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Rp885.000</t>
+          <t>Rp1.275.000</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
@@ -4687,16 +4687,16 @@
         <v>70</v>
       </c>
       <c r="D35" t="n">
-        <v>58</v>
+        <v>56</v>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>17.1%</t>
+          <t>20.0%</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Rp2.110.000</t>
+          <t>Rp2.370.000</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
@@ -4842,16 +4842,16 @@
         <v>54</v>
       </c>
       <c r="D40" t="n">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>24.1%</t>
+          <t>27.8%</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Rp2.390.000</t>
+          <t>Rp2.640.000</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
@@ -5121,16 +5121,16 @@
         <v>80</v>
       </c>
       <c r="D49" t="n">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>45.0%</t>
+          <t>46.2%</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Rp5.600.000</t>
+          <t>Rp5.725.000</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
@@ -5462,16 +5462,16 @@
         <v>32</v>
       </c>
       <c r="D60" t="n">
-        <v>28</v>
+        <v>25</v>
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>12.5%</t>
+          <t>21.9%</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Rp1.100.000</t>
+          <t>Rp1.885.000</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
@@ -5648,16 +5648,16 @@
         <v>102</v>
       </c>
       <c r="D66" t="n">
-        <v>87</v>
+        <v>83</v>
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>14.7%</t>
+          <t>18.6%</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Rp4.347.000</t>
+          <t>Rp5.535.000</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
@@ -5679,16 +5679,16 @@
         <v>234</v>
       </c>
       <c r="D67" t="n">
-        <v>147</v>
+        <v>145</v>
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>37.2%</t>
+          <t>38.0%</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Rp10.132.000</t>
+          <t>Rp10.310.000</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
@@ -5803,16 +5803,16 @@
         <v>30</v>
       </c>
       <c r="D71" t="n">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>43.3%</t>
+          <t>50.0%</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Rp4.765.000</t>
+          <t>Rp5.535.000</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
@@ -6040,16 +6040,16 @@
         <v>108</v>
       </c>
       <c r="D5" t="n">
-        <v>85</v>
+        <v>83</v>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>21.3%</t>
+          <t>23.1%</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Rp7.650.000</t>
+          <t>Rp8.250.000</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
@@ -6443,16 +6443,16 @@
         <v>34</v>
       </c>
       <c r="D18" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>38.2%</t>
+          <t>41.2%</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Rp2.300.000</t>
+          <t>Rp2.450.000</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
@@ -6618,16 +6618,16 @@
         <v>186</v>
       </c>
       <c r="D2" t="n">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>25.8%</t>
+          <t>25.3%</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Rp13.470.000</t>
+          <t>Rp13.390.000</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
@@ -6711,16 +6711,16 @@
         <v>90</v>
       </c>
       <c r="D5" t="n">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>5.6%</t>
+          <t>6.7%</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Rp565.000</t>
+          <t>Rp634.000</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
@@ -6742,16 +6742,16 @@
         <v>216</v>
       </c>
       <c r="D6" t="n">
-        <v>154</v>
+        <v>151</v>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>28.7%</t>
+          <t>30.1%</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Rp13.395.000</t>
+          <t>Rp13.935.000</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
@@ -6928,16 +6928,16 @@
         <v>54</v>
       </c>
       <c r="D12" t="n">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>29.6%</t>
+          <t>33.3%</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Rp3.050.000</t>
+          <t>Rp3.450.000</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
@@ -7052,16 +7052,16 @@
         <v>108</v>
       </c>
       <c r="D16" t="n">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>32.4%</t>
+          <t>33.3%</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Rp6.450.000</t>
+          <t>Rp6.550.000</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
@@ -7083,16 +7083,16 @@
         <v>144</v>
       </c>
       <c r="D17" t="n">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>9.0%</t>
+          <t>9.7%</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Rp2.800.000</t>
+          <t>Rp2.900.000</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
@@ -7176,16 +7176,16 @@
         <v>90</v>
       </c>
       <c r="D20" t="n">
-        <v>75</v>
+        <v>73</v>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>16.7%</t>
+          <t>18.9%</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Rp1.485.000</t>
+          <t>Rp1.683.000</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
@@ -7207,16 +7207,16 @@
         <v>153</v>
       </c>
       <c r="D21" t="n">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>52.9%</t>
+          <t>53.6%</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Rp26.300.000</t>
+          <t>Rp26.500.000</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
@@ -7362,16 +7362,16 @@
         <v>108</v>
       </c>
       <c r="D26" t="n">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>19.4%</t>
+          <t>20.4%</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Rp4.610.000</t>
+          <t>Rp4.780.000</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
@@ -7517,16 +7517,16 @@
         <v>96</v>
       </c>
       <c r="D31" t="n">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>22.9%</t>
+          <t>24.0%</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Rp3.290.000</t>
+          <t>Rp3.540.000</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
@@ -7641,16 +7641,16 @@
         <v>187</v>
       </c>
       <c r="D35" t="n">
-        <v>81</v>
+        <v>73</v>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>56.7%</t>
+          <t>61.0%</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Rp18.000.000</t>
+          <t>Rp18.575.000</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
@@ -7765,16 +7765,16 @@
         <v>34</v>
       </c>
       <c r="D39" t="n">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>26.5%</t>
+          <t>32.4%</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Rp2.092.000</t>
+          <t>Rp2.568.000</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
@@ -7827,16 +7827,16 @@
         <v>150</v>
       </c>
       <c r="D41" t="n">
-        <v>68</v>
+        <v>66</v>
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>54.7%</t>
+          <t>56.0%</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Rp24.700.000</t>
+          <t>Rp25.400.000</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
@@ -7858,16 +7858,16 @@
         <v>112</v>
       </c>
       <c r="D42" t="n">
-        <v>91</v>
+        <v>89</v>
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>18.8%</t>
+          <t>20.5%</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Rp8.200.000</t>
+          <t>Rp9.000.000</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
@@ -7951,16 +7951,16 @@
         <v>112</v>
       </c>
       <c r="D45" t="n">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>38.4%</t>
+          <t>39.3%</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Rp10.105.000</t>
+          <t>Rp10.330.000</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
@@ -7982,16 +7982,16 @@
         <v>174</v>
       </c>
       <c r="D46" t="n">
-        <v>105</v>
+        <v>101</v>
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>39.7%</t>
+          <t>42.0%</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Rp29.500.000</t>
+          <t>Rp31.300.000</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
@@ -8106,16 +8106,16 @@
         <v>102</v>
       </c>
       <c r="D50" t="n">
-        <v>90</v>
+        <v>75</v>
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>11.8%</t>
+          <t>26.5%</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Rp3.948.000</t>
+          <t>Rp8.583.000</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
@@ -8281,16 +8281,16 @@
         <v>76</v>
       </c>
       <c r="D2" t="n">
-        <v>66</v>
+        <v>64</v>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>13.2%</t>
+          <t>15.8%</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Rp1.250.000</t>
+          <t>Rp1.500.000</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
@@ -8321,7 +8321,7 @@
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Rp10.385.000</t>
+          <t>Rp10.135.000</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
@@ -8374,16 +8374,16 @@
         <v>86</v>
       </c>
       <c r="D5" t="n">
-        <v>65</v>
+        <v>63</v>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>24.4%</t>
+          <t>26.7%</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Rp6.050.000</t>
+          <t>Rp6.550.000</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
@@ -8405,16 +8405,16 @@
         <v>72</v>
       </c>
       <c r="D6" t="n">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>37.5%</t>
+          <t>36.1%</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Rp6.879.000</t>
+          <t>Rp6.704.000</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
@@ -8467,16 +8467,16 @@
         <v>51</v>
       </c>
       <c r="D8" t="n">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>19.6%</t>
+          <t>15.7%</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Rp1.535.000</t>
+          <t>Rp1.235.000</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
@@ -8560,16 +8560,16 @@
         <v>72</v>
       </c>
       <c r="D11" t="n">
-        <v>48</v>
+        <v>44</v>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>33.3%</t>
+          <t>38.9%</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Rp5.905.000</t>
+          <t>Rp6.895.000</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
@@ -8777,16 +8777,16 @@
         <v>48</v>
       </c>
       <c r="D18" t="n">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>41.7%</t>
+          <t>43.8%</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Rp4.580.000</t>
+          <t>Rp4.715.000</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
@@ -8839,16 +8839,16 @@
         <v>17</v>
       </c>
       <c r="D20" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>11.8%</t>
+          <t>17.6%</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Rp320.000</t>
+          <t>Rp480.000</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
@@ -8963,16 +8963,16 @@
         <v>54</v>
       </c>
       <c r="D24" t="n">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>55.6%</t>
+          <t>61.1%</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Rp4.274.993</t>
+          <t>Rp4.724.992</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
@@ -8994,16 +8994,16 @@
         <v>54</v>
       </c>
       <c r="D25" t="n">
-        <v>52</v>
+        <v>50</v>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>3.7%</t>
+          <t>7.4%</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Rp430.000</t>
+          <t>Rp1.000.000</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
@@ -9025,16 +9025,16 @@
         <v>54</v>
       </c>
       <c r="D26" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>68.5%</t>
+          <t>70.4%</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Rp5.550.000</t>
+          <t>Rp5.700.000</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
@@ -9211,16 +9211,16 @@
         <v>34</v>
       </c>
       <c r="D32" t="n">
-        <v>22</v>
+        <v>16</v>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>35.3%</t>
+          <t>52.9%</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Rp2.740.000</t>
+          <t>Rp3.970.000</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
@@ -9335,16 +9335,16 @@
         <v>72</v>
       </c>
       <c r="D36" t="n">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>30.6%</t>
+          <t>31.9%</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Rp1.982.000</t>
+          <t>Rp2.081.000</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
@@ -9397,16 +9397,16 @@
         <v>64</v>
       </c>
       <c r="D38" t="n">
-        <v>59</v>
+        <v>57</v>
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>7.8%</t>
+          <t>10.9%</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Rp713.000</t>
+          <t>Rp1.051.000</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
@@ -9459,16 +9459,16 @@
         <v>68</v>
       </c>
       <c r="D40" t="n">
-        <v>60</v>
+        <v>56</v>
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>11.8%</t>
+          <t>17.6%</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Rp1.434.000</t>
+          <t>Rp2.230.000</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">

--- a/laporan_padel_dki_jakarta_2026-10-30.xlsx
+++ b/laporan_padel_dki_jakarta_2026-10-30.xlsx
@@ -482,16 +482,16 @@
         <v>108</v>
       </c>
       <c r="D2" t="n">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>23.1%</t>
+          <t>24.1%</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Rp1.980.000</t>
+          <t>Rp2.060.000</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
@@ -513,16 +513,16 @@
         <v>68</v>
       </c>
       <c r="D3" t="n">
-        <v>49</v>
+        <v>47</v>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>27.9%</t>
+          <t>30.9%</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Rp2.683.000</t>
+          <t>Rp2.867.000</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
@@ -575,16 +575,16 @@
         <v>80</v>
       </c>
       <c r="D5" t="n">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>23.8%</t>
+          <t>25.0%</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Rp2.340.000</t>
+          <t>Rp2.490.000</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
@@ -730,16 +730,16 @@
         <v>72</v>
       </c>
       <c r="D10" t="n">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>33.3%</t>
+          <t>36.1%</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Rp5.855.990</t>
+          <t>Rp6.553.988</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
@@ -823,16 +823,16 @@
         <v>68</v>
       </c>
       <c r="D13" t="n">
-        <v>49</v>
+        <v>47</v>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>27.9%</t>
+          <t>30.9%</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Rp4.250.000</t>
+          <t>Rp4.750.000</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
@@ -854,16 +854,16 @@
         <v>162</v>
       </c>
       <c r="D14" t="n">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>33.3%</t>
+          <t>34.0%</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Rp11.519.500</t>
+          <t>Rp11.794.500</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
@@ -916,16 +916,16 @@
         <v>112</v>
       </c>
       <c r="D16" t="n">
-        <v>98</v>
+        <v>96</v>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>12.5%</t>
+          <t>14.3%</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Rp2.240.000</t>
+          <t>Rp2.740.000</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
@@ -1009,16 +1009,16 @@
         <v>108</v>
       </c>
       <c r="D19" t="n">
-        <v>79</v>
+        <v>76</v>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>26.9%</t>
+          <t>29.6%</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Rp5.130.000</t>
+          <t>Rp5.505.000</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
@@ -1040,16 +1040,16 @@
         <v>48</v>
       </c>
       <c r="D20" t="n">
-        <v>35</v>
+        <v>33</v>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>27.1%</t>
+          <t>31.2%</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Rp2.364.000</t>
+          <t>Rp2.802.000</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
@@ -1102,16 +1102,16 @@
         <v>136</v>
       </c>
       <c r="D22" t="n">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>28.7%</t>
+          <t>29.4%</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Rp12.914.000</t>
+          <t>Rp13.214.000</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
@@ -1133,16 +1133,16 @@
         <v>102</v>
       </c>
       <c r="D23" t="n">
-        <v>75</v>
+        <v>69</v>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>26.5%</t>
+          <t>32.4%</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Rp4.750.000</t>
+          <t>Rp5.900.000</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
@@ -1226,16 +1226,16 @@
         <v>68</v>
       </c>
       <c r="D26" t="n">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>14.7%</t>
+          <t>13.2%</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Rp1.615.000</t>
+          <t>Rp1.415.000</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
@@ -1536,16 +1536,16 @@
         <v>68</v>
       </c>
       <c r="D36" t="n">
-        <v>59</v>
+        <v>54</v>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>13.2%</t>
+          <t>20.6%</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Rp1.125.000</t>
+          <t>Rp1.750.000</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
@@ -1567,16 +1567,16 @@
         <v>72</v>
       </c>
       <c r="D37" t="n">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>44.4%</t>
+          <t>47.2%</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Rp4.975.000</t>
+          <t>Rp5.355.000</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
@@ -1753,16 +1753,16 @@
         <v>234</v>
       </c>
       <c r="D43" t="n">
-        <v>218</v>
+        <v>215</v>
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>6.8%</t>
+          <t>8.1%</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Rp3.787.000</t>
+          <t>Rp4.582.000</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
@@ -1846,16 +1846,16 @@
         <v>60</v>
       </c>
       <c r="D46" t="n">
-        <v>41</v>
+        <v>47</v>
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>31.7%</t>
+          <t>21.7%</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Rp3.264.000</t>
+          <t>Rp2.004.000</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
@@ -2094,16 +2094,16 @@
         <v>60</v>
       </c>
       <c r="D54" t="n">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>6.7%</t>
+          <t>8.3%</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Rp432.000</t>
+          <t>Rp528.000</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
@@ -2125,16 +2125,16 @@
         <v>32</v>
       </c>
       <c r="D55" t="n">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>9.4%</t>
+          <t>15.6%</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Rp450.000</t>
+          <t>Rp800.000</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
@@ -2156,16 +2156,16 @@
         <v>17</v>
       </c>
       <c r="D56" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>29.4%</t>
+          <t>35.3%</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Rp745.000</t>
+          <t>Rp945.000</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
@@ -2218,16 +2218,16 @@
         <v>54</v>
       </c>
       <c r="D58" t="n">
-        <v>45</v>
+        <v>43</v>
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>16.7%</t>
+          <t>20.4%</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Rp915.000</t>
+          <t>Rp1.140.000</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
@@ -2249,16 +2249,16 @@
         <v>32</v>
       </c>
       <c r="D59" t="n">
-        <v>29</v>
+        <v>25</v>
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>9.4%</t>
+          <t>21.9%</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Rp775.000</t>
+          <t>Rp1.875.000</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
@@ -2280,16 +2280,16 @@
         <v>36</v>
       </c>
       <c r="D60" t="n">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>5.6%</t>
+          <t>8.3%</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Rp298.000</t>
+          <t>Rp447.000</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
@@ -2373,16 +2373,16 @@
         <v>72</v>
       </c>
       <c r="D63" t="n">
-        <v>55</v>
+        <v>48</v>
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>23.6%</t>
+          <t>33.3%</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Rp2.355.000</t>
+          <t>Rp3.025.000</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
@@ -2435,16 +2435,16 @@
         <v>34</v>
       </c>
       <c r="D65" t="n">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>11.8%</t>
+          <t>14.7%</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Rp240.000</t>
+          <t>Rp390.000</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
@@ -2683,16 +2683,16 @@
         <v>72</v>
       </c>
       <c r="D73" t="n">
-        <v>65</v>
+        <v>56</v>
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>9.7%</t>
+          <t>22.2%</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Rp620.000</t>
+          <t>Rp2.150.000</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
@@ -2745,16 +2745,16 @@
         <v>96</v>
       </c>
       <c r="D75" t="n">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>14.6%</t>
+          <t>15.6%</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Rp2.640.000</t>
+          <t>Rp2.900.000</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
@@ -2776,16 +2776,16 @@
         <v>98</v>
       </c>
       <c r="D76" t="n">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>12.2%</t>
+          <t>13.3%</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Rp2.350.000</t>
+          <t>Rp2.650.000</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
@@ -2807,16 +2807,16 @@
         <v>45</v>
       </c>
       <c r="D77" t="n">
-        <v>31</v>
+        <v>27</v>
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>31.1%</t>
+          <t>40.0%</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Rp2.100.000</t>
+          <t>Rp2.700.000</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
@@ -2838,16 +2838,16 @@
         <v>128</v>
       </c>
       <c r="D78" t="n">
-        <v>96</v>
+        <v>99</v>
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>25.0%</t>
+          <t>22.7%</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>Rp6.225.000</t>
+          <t>Rp5.640.000</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
@@ -2869,16 +2869,16 @@
         <v>108</v>
       </c>
       <c r="D79" t="n">
-        <v>92</v>
+        <v>87</v>
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>14.8%</t>
+          <t>19.4%</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>Rp1.800.000</t>
+          <t>Rp2.400.000</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
@@ -2900,16 +2900,16 @@
         <v>114</v>
       </c>
       <c r="D80" t="n">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>4.4%</t>
+          <t>5.3%</t>
         </is>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>Rp1.850.000</t>
+          <t>Rp2.350.000</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
@@ -2931,16 +2931,16 @@
         <v>126</v>
       </c>
       <c r="D81" t="n">
-        <v>100</v>
+        <v>97</v>
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>20.6%</t>
+          <t>23.0%</t>
         </is>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>Rp3.774.000</t>
+          <t>Rp4.371.000</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
@@ -3055,16 +3055,16 @@
         <v>135</v>
       </c>
       <c r="D85" t="n">
-        <v>111</v>
+        <v>108</v>
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>17.8%</t>
+          <t>20.0%</t>
         </is>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>Rp5.040.000</t>
+          <t>Rp5.715.000</t>
         </is>
       </c>
       <c r="G85" t="inlineStr">
@@ -3179,16 +3179,16 @@
         <v>138</v>
       </c>
       <c r="D89" t="n">
-        <v>111</v>
+        <v>106</v>
       </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t>19.6%</t>
+          <t>23.2%</t>
         </is>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>Rp5.075.000</t>
+          <t>Rp6.200.000</t>
         </is>
       </c>
       <c r="G89" t="inlineStr">
@@ -3241,16 +3241,16 @@
         <v>119</v>
       </c>
       <c r="D91" t="n">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="E91" t="inlineStr">
         <is>
-          <t>14.3%</t>
+          <t>15.1%</t>
         </is>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>Rp2.660.000</t>
+          <t>Rp2.840.000</t>
         </is>
       </c>
       <c r="G91" t="inlineStr">
@@ -3303,16 +3303,16 @@
         <v>42</v>
       </c>
       <c r="D93" t="n">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="E93" t="inlineStr">
         <is>
-          <t>16.7%</t>
+          <t>19.0%</t>
         </is>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>Rp693.000</t>
+          <t>Rp792.000</t>
         </is>
       </c>
       <c r="G93" t="inlineStr">
@@ -3396,16 +3396,16 @@
         <v>80</v>
       </c>
       <c r="D96" t="n">
-        <v>58</v>
+        <v>64</v>
       </c>
       <c r="E96" t="inlineStr">
         <is>
-          <t>27.5%</t>
+          <t>20.0%</t>
         </is>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>Rp4.278.000</t>
+          <t>Rp2.784.000</t>
         </is>
       </c>
       <c r="G96" t="inlineStr">
@@ -3458,16 +3458,16 @@
         <v>112</v>
       </c>
       <c r="D98" t="n">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="E98" t="inlineStr">
         <is>
-          <t>15.2%</t>
+          <t>16.1%</t>
         </is>
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>Rp1.880.000</t>
+          <t>Rp2.080.000</t>
         </is>
       </c>
       <c r="G98" t="inlineStr">
@@ -3664,16 +3664,16 @@
         <v>36</v>
       </c>
       <c r="D2" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>44.4%</t>
+          <t>47.2%</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Rp1.296.000</t>
+          <t>Rp1.377.000</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
@@ -3695,16 +3695,16 @@
         <v>126</v>
       </c>
       <c r="D3" t="n">
-        <v>63</v>
+        <v>65</v>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>50.0%</t>
+          <t>48.4%</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Rp15.460.000</t>
+          <t>Rp14.912.500</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
@@ -3757,16 +3757,16 @@
         <v>96</v>
       </c>
       <c r="D5" t="n">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>18.8%</t>
+          <t>19.8%</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Rp4.700.000</t>
+          <t>Rp5.050.000</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
@@ -3819,16 +3819,16 @@
         <v>162</v>
       </c>
       <c r="D7" t="n">
-        <v>117</v>
+        <v>111</v>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>27.8%</t>
+          <t>31.5%</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Rp7.365.000</t>
+          <t>Rp8.415.000</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
@@ -4036,16 +4036,16 @@
         <v>70</v>
       </c>
       <c r="D14" t="n">
-        <v>47</v>
+        <v>45</v>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>32.9%</t>
+          <t>35.7%</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Rp2.296.000</t>
+          <t>Rp2.496.000</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
@@ -4129,16 +4129,16 @@
         <v>65</v>
       </c>
       <c r="D17" t="n">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>23.1%</t>
+          <t>24.6%</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Rp6.525.000</t>
+          <t>Rp6.930.000</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
@@ -4284,16 +4284,16 @@
         <v>34</v>
       </c>
       <c r="D22" t="n">
-        <v>27</v>
+        <v>24</v>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>20.6%</t>
+          <t>29.4%</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Rp1.275.000</t>
+          <t>Rp1.860.000</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
@@ -4315,16 +4315,16 @@
         <v>36</v>
       </c>
       <c r="D23" t="n">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>16.7%</t>
+          <t>13.9%</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Rp1.680.000</t>
+          <t>Rp1.175.000</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
@@ -4625,16 +4625,16 @@
         <v>90</v>
       </c>
       <c r="D33" t="n">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>33.3%</t>
+          <t>34.4%</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Rp5.900.000</t>
+          <t>Rp6.125.000</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
@@ -5121,16 +5121,16 @@
         <v>80</v>
       </c>
       <c r="D49" t="n">
-        <v>43</v>
+        <v>47</v>
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>46.2%</t>
+          <t>41.2%</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Rp5.725.000</t>
+          <t>Rp4.825.000</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
@@ -5183,16 +5183,16 @@
         <v>72</v>
       </c>
       <c r="D51" t="n">
-        <v>66</v>
+        <v>69</v>
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>8.3%</t>
+          <t>4.2%</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Rp2.376.000</t>
+          <t>Rp1.188.000</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
@@ -5369,16 +5369,16 @@
         <v>75</v>
       </c>
       <c r="D57" t="n">
-        <v>72</v>
+        <v>70</v>
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>4.0%</t>
+          <t>6.7%</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Rp195.000</t>
+          <t>Rp319.000</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
@@ -5400,16 +5400,16 @@
         <v>51</v>
       </c>
       <c r="D58" t="n">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>23.5%</t>
+          <t>25.5%</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Rp2.000.000</t>
+          <t>Rp2.175.000</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
@@ -5462,16 +5462,16 @@
         <v>32</v>
       </c>
       <c r="D60" t="n">
-        <v>25</v>
+        <v>29</v>
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>21.9%</t>
+          <t>9.4%</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Rp1.885.000</t>
+          <t>Rp785.000</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
@@ -5617,16 +5617,16 @@
         <v>90</v>
       </c>
       <c r="D65" t="n">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>33.3%</t>
+          <t>34.4%</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Rp10.350.000</t>
+          <t>Rp10.750.000</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
@@ -5648,16 +5648,16 @@
         <v>102</v>
       </c>
       <c r="D66" t="n">
-        <v>83</v>
+        <v>80</v>
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>18.6%</t>
+          <t>21.6%</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Rp5.535.000</t>
+          <t>Rp6.426.000</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
@@ -5679,16 +5679,16 @@
         <v>234</v>
       </c>
       <c r="D67" t="n">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>38.0%</t>
+          <t>38.5%</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Rp10.310.000</t>
+          <t>Rp10.400.000</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
@@ -5710,16 +5710,16 @@
         <v>84</v>
       </c>
       <c r="D68" t="n">
-        <v>53</v>
+        <v>58</v>
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>36.9%</t>
+          <t>31.0%</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Rp9.155.000</t>
+          <t>Rp7.405.000</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
@@ -5741,16 +5741,16 @@
         <v>144</v>
       </c>
       <c r="D69" t="n">
-        <v>112</v>
+        <v>110</v>
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>22.2%</t>
+          <t>23.6%</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Rp14.500.000</t>
+          <t>Rp15.500.000</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
@@ -5834,16 +5834,16 @@
         <v>162</v>
       </c>
       <c r="D72" t="n">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>29.6%</t>
+          <t>29.0%</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Rp23.200.000</t>
+          <t>Rp22.650.000</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
@@ -5865,16 +5865,16 @@
         <v>90</v>
       </c>
       <c r="D73" t="n">
-        <v>83</v>
+        <v>80</v>
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>7.8%</t>
+          <t>11.1%</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Rp2.550.000</t>
+          <t>Rp3.800.000</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
@@ -6009,16 +6009,16 @@
         <v>30</v>
       </c>
       <c r="D4" t="n">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>33.3%</t>
+          <t>40.0%</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Rp1.375.000</t>
+          <t>Rp1.750.000</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
@@ -6040,16 +6040,16 @@
         <v>108</v>
       </c>
       <c r="D5" t="n">
-        <v>83</v>
+        <v>78</v>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>23.1%</t>
+          <t>27.8%</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Rp8.250.000</t>
+          <t>Rp9.800.000</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
@@ -6133,16 +6133,16 @@
         <v>256</v>
       </c>
       <c r="D8" t="n">
-        <v>192</v>
+        <v>190</v>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>25.0%</t>
+          <t>25.8%</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Rp27.150.000</t>
+          <t>Rp28.750.000</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
@@ -6164,16 +6164,16 @@
         <v>54</v>
       </c>
       <c r="D9" t="n">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>33.3%</t>
+          <t>37.0%</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Rp3.275.000</t>
+          <t>Rp3.675.000</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
@@ -6257,16 +6257,16 @@
         <v>36</v>
       </c>
       <c r="D12" t="n">
-        <v>29</v>
+        <v>25</v>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>19.4%</t>
+          <t>30.6%</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Rp1.138.000</t>
+          <t>Rp1.956.000</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
@@ -6350,16 +6350,16 @@
         <v>51</v>
       </c>
       <c r="D15" t="n">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>52.9%</t>
+          <t>56.9%</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Rp4.800.000</t>
+          <t>Rp5.250.000</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
@@ -6381,16 +6381,16 @@
         <v>54</v>
       </c>
       <c r="D16" t="n">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>48.1%</t>
+          <t>51.9%</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Rp4.845.000</t>
+          <t>Rp5.415.000</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
@@ -6505,16 +6505,16 @@
         <v>15</v>
       </c>
       <c r="D20" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>6.7%</t>
+          <t>13.3%</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Rp228.000</t>
+          <t>Rp456.000</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
@@ -6618,16 +6618,16 @@
         <v>186</v>
       </c>
       <c r="D2" t="n">
-        <v>139</v>
+        <v>141</v>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>25.3%</t>
+          <t>24.2%</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Rp13.390.000</t>
+          <t>Rp13.250.000</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
@@ -6649,16 +6649,16 @@
         <v>96</v>
       </c>
       <c r="D3" t="n">
-        <v>86</v>
+        <v>84</v>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>10.4%</t>
+          <t>12.5%</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Rp6.200.000</t>
+          <t>Rp6.400.000</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
@@ -6711,16 +6711,16 @@
         <v>90</v>
       </c>
       <c r="D5" t="n">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>6.7%</t>
+          <t>7.8%</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Rp634.000</t>
+          <t>Rp703.000</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
@@ -6773,16 +6773,16 @@
         <v>144</v>
       </c>
       <c r="D7" t="n">
-        <v>119</v>
+        <v>117</v>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>17.4%</t>
+          <t>18.8%</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Rp7.375.000</t>
+          <t>Rp8.075.000</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
@@ -6804,16 +6804,16 @@
         <v>54</v>
       </c>
       <c r="D8" t="n">
-        <v>50</v>
+        <v>52</v>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>7.4%</t>
+          <t>3.7%</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Rp1.000.000</t>
+          <t>Rp500.000</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
@@ -6835,16 +6835,16 @@
         <v>90</v>
       </c>
       <c r="D9" t="n">
-        <v>48</v>
+        <v>42</v>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>46.7%</t>
+          <t>53.3%</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Rp8.773.000</t>
+          <t>Rp9.439.000</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
@@ -6897,16 +6897,16 @@
         <v>216</v>
       </c>
       <c r="D11" t="n">
-        <v>165</v>
+        <v>162</v>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>23.6%</t>
+          <t>25.0%</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Rp12.598.000</t>
+          <t>Rp13.438.000</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
@@ -6990,16 +6990,16 @@
         <v>72</v>
       </c>
       <c r="D14" t="n">
-        <v>63</v>
+        <v>60</v>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>12.5%</t>
+          <t>16.7%</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Rp2.205.000</t>
+          <t>Rp3.030.000</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
@@ -7052,16 +7052,16 @@
         <v>108</v>
       </c>
       <c r="D16" t="n">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>33.3%</t>
+          <t>34.3%</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Rp6.550.000</t>
+          <t>Rp6.750.000</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
@@ -7083,16 +7083,16 @@
         <v>144</v>
       </c>
       <c r="D17" t="n">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>9.7%</t>
+          <t>9.0%</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Rp2.900.000</t>
+          <t>Rp2.625.000</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
@@ -7145,16 +7145,16 @@
         <v>39</v>
       </c>
       <c r="D19" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>41.0%</t>
+          <t>43.6%</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Rp3.811.000</t>
+          <t>Rp4.349.000</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
@@ -7269,21 +7269,21 @@
         <v>126</v>
       </c>
       <c r="D23" t="n">
-        <v>91</v>
+        <v>100</v>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>27.8%</t>
+          <t>20.6%</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Rp5.505.000</t>
+          <t>Rp3.930.000</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Rp81.000 - Rp175.000</t>
+          <t>Rp10.000 - Rp175.000</t>
         </is>
       </c>
     </row>
@@ -7300,16 +7300,16 @@
         <v>90</v>
       </c>
       <c r="D24" t="n">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>28.9%</t>
+          <t>30.0%</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Rp5.160.000</t>
+          <t>Rp5.415.000</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
@@ -7362,16 +7362,16 @@
         <v>108</v>
       </c>
       <c r="D26" t="n">
-        <v>86</v>
+        <v>83</v>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>20.4%</t>
+          <t>23.1%</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Rp4.780.000</t>
+          <t>Rp5.530.000</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
@@ -7517,16 +7517,16 @@
         <v>96</v>
       </c>
       <c r="D31" t="n">
-        <v>73</v>
+        <v>71</v>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>24.0%</t>
+          <t>26.0%</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Rp3.540.000</t>
+          <t>Rp4.040.000</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
@@ -7579,16 +7579,16 @@
         <v>72</v>
       </c>
       <c r="D33" t="n">
-        <v>63</v>
+        <v>67</v>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>12.5%</t>
+          <t>6.9%</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Rp2.405.000</t>
+          <t>Rp1.265.000</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
@@ -7610,16 +7610,16 @@
         <v>108</v>
       </c>
       <c r="D34" t="n">
-        <v>85</v>
+        <v>82</v>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>21.3%</t>
+          <t>24.1%</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Rp5.135.000</t>
+          <t>Rp5.870.000</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
@@ -7641,16 +7641,16 @@
         <v>187</v>
       </c>
       <c r="D35" t="n">
-        <v>73</v>
+        <v>71</v>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>61.0%</t>
+          <t>62.0%</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Rp18.575.000</t>
+          <t>Rp18.675.000</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
@@ -7827,16 +7827,16 @@
         <v>150</v>
       </c>
       <c r="D41" t="n">
-        <v>66</v>
+        <v>61</v>
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>56.0%</t>
+          <t>59.3%</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Rp25.400.000</t>
+          <t>Rp27.000.000</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
@@ -7858,16 +7858,16 @@
         <v>112</v>
       </c>
       <c r="D42" t="n">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>20.5%</t>
+          <t>19.6%</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Rp9.000.000</t>
+          <t>Rp8.600.000</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
@@ -7889,16 +7889,16 @@
         <v>80</v>
       </c>
       <c r="D43" t="n">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>50.0%</t>
+          <t>51.2%</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Rp6.050.000</t>
+          <t>Rp6.225.000</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
@@ -7951,16 +7951,16 @@
         <v>112</v>
       </c>
       <c r="D45" t="n">
-        <v>68</v>
+        <v>66</v>
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>39.3%</t>
+          <t>41.1%</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Rp10.330.000</t>
+          <t>Rp10.705.000</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
@@ -7982,16 +7982,16 @@
         <v>174</v>
       </c>
       <c r="D46" t="n">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>42.0%</t>
+          <t>42.5%</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Rp31.300.000</t>
+          <t>Rp32.000.000</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
@@ -8199,16 +8199,16 @@
         <v>90</v>
       </c>
       <c r="D53" t="n">
-        <v>76</v>
+        <v>72</v>
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>15.6%</t>
+          <t>20.0%</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Rp3.200.000</t>
+          <t>Rp4.400.000</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
@@ -8281,16 +8281,16 @@
         <v>76</v>
       </c>
       <c r="D2" t="n">
-        <v>64</v>
+        <v>62</v>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>15.8%</t>
+          <t>18.4%</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Rp1.500.000</t>
+          <t>Rp1.750.000</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
@@ -8312,16 +8312,16 @@
         <v>136</v>
       </c>
       <c r="D3" t="n">
-        <v>73</v>
+        <v>70</v>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>46.3%</t>
+          <t>48.5%</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Rp10.135.000</t>
+          <t>Rp10.615.000</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
@@ -8374,16 +8374,16 @@
         <v>86</v>
       </c>
       <c r="D5" t="n">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>26.7%</t>
+          <t>27.9%</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Rp6.550.000</t>
+          <t>Rp6.900.000</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
@@ -8436,16 +8436,16 @@
         <v>51</v>
       </c>
       <c r="D7" t="n">
-        <v>32</v>
+        <v>28</v>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>37.3%</t>
+          <t>45.1%</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Rp3.820.000</t>
+          <t>Rp4.670.000</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
@@ -8467,16 +8467,16 @@
         <v>51</v>
       </c>
       <c r="D8" t="n">
-        <v>43</v>
+        <v>39</v>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>15.7%</t>
+          <t>23.5%</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Rp1.235.000</t>
+          <t>Rp1.940.000</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
@@ -8560,16 +8560,16 @@
         <v>72</v>
       </c>
       <c r="D11" t="n">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>38.9%</t>
+          <t>41.7%</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Rp6.895.000</t>
+          <t>Rp7.365.000</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
@@ -8715,16 +8715,16 @@
         <v>54</v>
       </c>
       <c r="D16" t="n">
-        <v>34</v>
+        <v>37</v>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>37.0%</t>
+          <t>31.5%</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Rp5.100.000</t>
+          <t>Rp4.230.000</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
@@ -8777,16 +8777,16 @@
         <v>48</v>
       </c>
       <c r="D18" t="n">
-        <v>27</v>
+        <v>21</v>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>43.8%</t>
+          <t>56.2%</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Rp4.715.000</t>
+          <t>Rp6.355.000</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
@@ -8808,16 +8808,16 @@
         <v>108</v>
       </c>
       <c r="D19" t="n">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>68.5%</t>
+          <t>69.4%</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Rp27.510.000</t>
+          <t>Rp27.990.000</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
@@ -8901,16 +8901,16 @@
         <v>144</v>
       </c>
       <c r="D22" t="n">
-        <v>122</v>
+        <v>120</v>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>15.3%</t>
+          <t>16.7%</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Rp4.245.000</t>
+          <t>Rp4.635.000</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
@@ -9149,16 +9149,16 @@
         <v>54</v>
       </c>
       <c r="D30" t="n">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>33.3%</t>
+          <t>35.2%</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Rp3.450.000</t>
+          <t>Rp3.675.000</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
@@ -9180,16 +9180,16 @@
         <v>54</v>
       </c>
       <c r="D31" t="n">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>29.6%</t>
+          <t>33.3%</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Rp4.245.000</t>
+          <t>Rp4.809.000</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
@@ -9211,16 +9211,16 @@
         <v>34</v>
       </c>
       <c r="D32" t="n">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>52.9%</t>
+          <t>47.1%</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Rp3.970.000</t>
+          <t>Rp3.520.000</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
@@ -9242,16 +9242,16 @@
         <v>36</v>
       </c>
       <c r="D33" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>50.0%</t>
+          <t>52.8%</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Rp2.900.000</t>
+          <t>Rp3.000.000</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
@@ -9273,16 +9273,16 @@
         <v>144</v>
       </c>
       <c r="D34" t="n">
-        <v>115</v>
+        <v>117</v>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>20.1%</t>
+          <t>18.8%</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Rp5.295.000</t>
+          <t>Rp4.513.000</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
@@ -9335,16 +9335,16 @@
         <v>72</v>
       </c>
       <c r="D36" t="n">
-        <v>49</v>
+        <v>47</v>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>31.9%</t>
+          <t>34.7%</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Rp2.081.000</t>
+          <t>Rp2.279.000</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
@@ -9397,16 +9397,16 @@
         <v>64</v>
       </c>
       <c r="D38" t="n">
-        <v>57</v>
+        <v>54</v>
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>10.9%</t>
+          <t>15.6%</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Rp1.051.000</t>
+          <t>Rp1.558.000</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
@@ -9459,16 +9459,16 @@
         <v>68</v>
       </c>
       <c r="D40" t="n">
-        <v>56</v>
+        <v>54</v>
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>17.6%</t>
+          <t>20.6%</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Rp2.230.000</t>
+          <t>Rp2.628.000</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
@@ -9490,16 +9490,16 @@
         <v>64</v>
       </c>
       <c r="D41" t="n">
-        <v>47</v>
+        <v>45</v>
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>26.6%</t>
+          <t>29.7%</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Rp3.200.000</t>
+          <t>Rp3.600.000</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">

--- a/laporan_padel_dki_jakarta_2026-10-30.xlsx
+++ b/laporan_padel_dki_jakarta_2026-10-30.xlsx
@@ -730,16 +730,16 @@
         <v>72</v>
       </c>
       <c r="D10" t="n">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>36.1%</t>
+          <t>33.3%</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Rp6.553.988</t>
+          <t>Rp6.215.988</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
@@ -978,16 +978,16 @@
         <v>117</v>
       </c>
       <c r="D18" t="n">
-        <v>96</v>
+        <v>94</v>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>17.9%</t>
+          <t>19.7%</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Rp3.000.000</t>
+          <t>Rp3.200.000</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
@@ -1071,16 +1071,16 @@
         <v>136</v>
       </c>
       <c r="D21" t="n">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>28.7%</t>
+          <t>29.4%</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Rp11.050.000</t>
+          <t>Rp11.355.000</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
@@ -1195,16 +1195,16 @@
         <v>72</v>
       </c>
       <c r="D25" t="n">
-        <v>55</v>
+        <v>51</v>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>23.6%</t>
+          <t>29.2%</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Rp3.075.000</t>
+          <t>Rp4.075.000</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
@@ -1350,16 +1350,16 @@
         <v>54</v>
       </c>
       <c r="D30" t="n">
-        <v>46</v>
+        <v>42</v>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>14.8%</t>
+          <t>22.2%</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Rp1.880.000</t>
+          <t>Rp2.840.000</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
@@ -1474,16 +1474,16 @@
         <v>68</v>
       </c>
       <c r="D34" t="n">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>27.9%</t>
+          <t>29.4%</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Rp3.845.000</t>
+          <t>Rp4.005.000</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
@@ -1660,16 +1660,16 @@
         <v>72</v>
       </c>
       <c r="D40" t="n">
-        <v>64</v>
+        <v>62</v>
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>11.1%</t>
+          <t>13.9%</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Rp1.680.000</t>
+          <t>Rp1.980.000</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
@@ -1722,16 +1722,16 @@
         <v>51</v>
       </c>
       <c r="D42" t="n">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>29.4%</t>
+          <t>27.5%</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Rp2.105.000</t>
+          <t>Rp2.020.000</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
@@ -1784,16 +1784,16 @@
         <v>76</v>
       </c>
       <c r="D44" t="n">
-        <v>50</v>
+        <v>44</v>
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>34.2%</t>
+          <t>42.1%</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Rp8.848.000</t>
+          <t>Rp10.148.000</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
@@ -2373,16 +2373,16 @@
         <v>72</v>
       </c>
       <c r="D63" t="n">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>33.3%</t>
+          <t>36.1%</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Rp3.025.000</t>
+          <t>Rp3.185.000</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
@@ -2931,16 +2931,16 @@
         <v>126</v>
       </c>
       <c r="D81" t="n">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>23.0%</t>
+          <t>23.8%</t>
         </is>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>Rp4.371.000</t>
+          <t>Rp4.470.000</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
@@ -2962,16 +2962,16 @@
         <v>54</v>
       </c>
       <c r="D82" t="n">
-        <v>43</v>
+        <v>40</v>
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>20.4%</t>
+          <t>25.9%</t>
         </is>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>Rp1.089.000</t>
+          <t>Rp1.386.000</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
@@ -3458,16 +3458,16 @@
         <v>112</v>
       </c>
       <c r="D98" t="n">
-        <v>94</v>
+        <v>90</v>
       </c>
       <c r="E98" t="inlineStr">
         <is>
-          <t>16.1%</t>
+          <t>19.6%</t>
         </is>
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>Rp2.080.000</t>
+          <t>Rp2.980.000</t>
         </is>
       </c>
       <c r="G98" t="inlineStr">
@@ -4098,16 +4098,16 @@
         <v>105</v>
       </c>
       <c r="D16" t="n">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>19.0%</t>
+          <t>20.0%</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Rp8.400.000</t>
+          <t>Rp8.750.000</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
@@ -4563,16 +4563,16 @@
         <v>72</v>
       </c>
       <c r="D31" t="n">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>2.8%</t>
+          <t>4.2%</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Rp400.000</t>
+          <t>Rp600.000</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
@@ -4625,16 +4625,16 @@
         <v>90</v>
       </c>
       <c r="D33" t="n">
-        <v>59</v>
+        <v>55</v>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>34.4%</t>
+          <t>38.9%</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Rp6.125.000</t>
+          <t>Rp6.725.000</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
@@ -4749,16 +4749,16 @@
         <v>159</v>
       </c>
       <c r="D37" t="n">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>42.8%</t>
+          <t>43.4%</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Rp23.200.000</t>
+          <t>Rp23.350.000</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
@@ -4873,16 +4873,16 @@
         <v>52</v>
       </c>
       <c r="D41" t="n">
-        <v>37</v>
+        <v>35</v>
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>28.8%</t>
+          <t>32.7%</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Rp4.500.000</t>
+          <t>Rp5.100.000</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
@@ -4966,16 +4966,16 @@
         <v>77</v>
       </c>
       <c r="D44" t="n">
-        <v>55</v>
+        <v>53</v>
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>28.6%</t>
+          <t>31.2%</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Rp8.410.000</t>
+          <t>Rp9.060.000</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
@@ -5276,16 +5276,16 @@
         <v>72</v>
       </c>
       <c r="D54" t="n">
-        <v>70</v>
+        <v>68</v>
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>2.8%</t>
+          <t>5.6%</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Rp400.000</t>
+          <t>Rp1.120.000</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
@@ -5617,16 +5617,16 @@
         <v>90</v>
       </c>
       <c r="D65" t="n">
-        <v>59</v>
+        <v>57</v>
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>34.4%</t>
+          <t>36.7%</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Rp10.750.000</t>
+          <t>Rp11.250.000</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
@@ -6040,16 +6040,16 @@
         <v>108</v>
       </c>
       <c r="D5" t="n">
-        <v>78</v>
+        <v>76</v>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>27.8%</t>
+          <t>29.6%</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Rp9.800.000</t>
+          <t>Rp10.300.000</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
@@ -6649,16 +6649,16 @@
         <v>96</v>
       </c>
       <c r="D3" t="n">
-        <v>84</v>
+        <v>82</v>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>12.5%</t>
+          <t>14.6%</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Rp6.400.000</t>
+          <t>Rp6.900.000</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
@@ -7021,16 +7021,16 @@
         <v>102</v>
       </c>
       <c r="D15" t="n">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>20.6%</t>
+          <t>21.6%</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Rp4.365.000</t>
+          <t>Rp4.565.000</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
@@ -7207,16 +7207,16 @@
         <v>153</v>
       </c>
       <c r="D21" t="n">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>53.6%</t>
+          <t>54.2%</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Rp26.500.000</t>
+          <t>Rp26.700.000</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
@@ -7269,16 +7269,16 @@
         <v>126</v>
       </c>
       <c r="D23" t="n">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>20.6%</t>
+          <t>21.4%</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Rp3.930.000</t>
+          <t>Rp4.011.000</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
@@ -7641,16 +7641,16 @@
         <v>187</v>
       </c>
       <c r="D35" t="n">
-        <v>71</v>
+        <v>69</v>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>62.0%</t>
+          <t>63.1%</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Rp18.675.000</t>
+          <t>Rp18.825.000</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
@@ -7703,16 +7703,16 @@
         <v>94</v>
       </c>
       <c r="D37" t="n">
-        <v>87</v>
+        <v>85</v>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>7.4%</t>
+          <t>9.6%</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Rp1.995.000</t>
+          <t>Rp2.393.000</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
@@ -7734,16 +7734,16 @@
         <v>170</v>
       </c>
       <c r="D38" t="n">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>27.1%</t>
+          <t>27.6%</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Rp5.900.000</t>
+          <t>Rp5.950.000</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
@@ -8312,16 +8312,16 @@
         <v>136</v>
       </c>
       <c r="D3" t="n">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>48.5%</t>
+          <t>49.3%</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Rp10.615.000</t>
+          <t>Rp10.740.000</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
@@ -8436,16 +8436,16 @@
         <v>51</v>
       </c>
       <c r="D7" t="n">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>45.1%</t>
+          <t>47.1%</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Rp4.670.000</t>
+          <t>Rp4.820.000</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
@@ -8560,16 +8560,16 @@
         <v>72</v>
       </c>
       <c r="D11" t="n">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>41.7%</t>
+          <t>44.4%</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Rp7.365.000</t>
+          <t>Rp7.780.000</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
@@ -8653,16 +8653,16 @@
         <v>72</v>
       </c>
       <c r="D14" t="n">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>19.4%</t>
+          <t>20.8%</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Rp2.450.000</t>
+          <t>Rp2.550.000</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
@@ -9273,16 +9273,16 @@
         <v>144</v>
       </c>
       <c r="D34" t="n">
-        <v>117</v>
+        <v>115</v>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>18.8%</t>
+          <t>20.1%</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Rp4.513.000</t>
+          <t>Rp4.711.000</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
@@ -9335,16 +9335,16 @@
         <v>72</v>
       </c>
       <c r="D36" t="n">
-        <v>47</v>
+        <v>45</v>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>34.7%</t>
+          <t>37.5%</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Rp2.279.000</t>
+          <t>Rp2.477.000</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
@@ -9366,16 +9366,16 @@
         <v>54</v>
       </c>
       <c r="D37" t="n">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>33.3%</t>
+          <t>35.2%</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Rp3.610.000</t>
+          <t>Rp3.760.000</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
